--- a/2022 data/excel_outputs/54_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/54_boothwise_data.xlsx
@@ -14,11 +14,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="591">
   <si>
     <t>AC 54 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -778,7 +847,7 @@
     <t>PRIMARY SCHOOL GULDHAR ROOM-1</t>
   </si>
   <si>
-    <t>PRIMARY SCHOOL GULDHAR ■■■■-2</t>
+    <t>MAHRISHI DAYANAND VIDHAPITH INTER COLLEGE GOVINDPURAM</t>
   </si>
   <si>
     <t>PRIMARY SCHOOL GULDHAR ROOM-3</t>
@@ -1724,8 +1793,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1741,7 +1818,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1749,12 +1826,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2053,82 +2148,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>547</v>
+        <v>570</v>
       </c>
       <c r="D2" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="E2" t="s">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="F2" t="s">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="G2" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
       <c r="H2" t="s">
-        <v>552</v>
+        <v>575</v>
       </c>
       <c r="I2" t="s">
-        <v>553</v>
+        <v>576</v>
       </c>
       <c r="J2" t="s">
-        <v>554</v>
+        <v>577</v>
       </c>
       <c r="K2" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="L2" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="M2" t="s">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="N2" t="s">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="O2" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="P2" t="s">
-        <v>560</v>
+        <v>583</v>
       </c>
       <c r="Q2" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="R2" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="S2" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
       <c r="T2" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="U2" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="V2" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="W2" t="s">
-        <v>566</v>
+        <v>589</v>
       </c>
       <c r="X2" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -2136,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2210,7 +2374,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2284,7 +2448,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2358,7 +2522,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2432,7 +2596,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2506,7 +2670,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2580,7 +2744,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2654,7 +2818,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2728,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2802,7 +2966,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2876,7 +3040,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2950,7 +3114,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -3024,7 +3188,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3098,7 +3262,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -3172,7 +3336,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3246,7 +3410,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3320,7 +3484,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3394,7 +3558,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3468,7 +3632,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3542,7 +3706,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3616,7 +3780,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3690,7 +3854,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3764,7 +3928,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3838,7 +4002,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3912,7 +4076,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3986,7 +4150,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4060,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -4134,7 +4298,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -4208,7 +4372,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4282,7 +4446,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -4356,7 +4520,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -4430,7 +4594,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4504,7 +4668,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4578,7 +4742,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4652,7 +4816,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4726,7 +4890,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -4800,7 +4964,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -4874,7 +5038,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -4948,7 +5112,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -5022,7 +5186,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -5096,7 +5260,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -5170,7 +5334,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -5244,7 +5408,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5318,7 +5482,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -5392,7 +5556,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -5466,7 +5630,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -5540,7 +5704,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -5614,7 +5778,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -5688,7 +5852,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5762,7 +5926,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5836,7 +6000,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5910,7 +6074,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5984,7 +6148,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -6058,7 +6222,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -6132,7 +6296,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -6206,7 +6370,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -6280,7 +6444,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -6354,7 +6518,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -6428,7 +6592,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -6502,7 +6666,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -6576,7 +6740,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -6650,7 +6814,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -6724,7 +6888,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6798,7 +6962,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6872,7 +7036,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6946,7 +7110,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -7020,7 +7184,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -7094,7 +7258,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -7168,7 +7332,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -7242,7 +7406,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -7316,7 +7480,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -7390,7 +7554,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -7464,7 +7628,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7538,7 +7702,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -7612,7 +7776,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -7686,7 +7850,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7760,7 +7924,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -7834,7 +7998,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -7908,7 +8072,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -7982,7 +8146,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -8056,7 +8220,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -8130,7 +8294,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -8204,7 +8368,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -8278,7 +8442,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -8352,7 +8516,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -8426,7 +8590,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -8500,7 +8664,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -8574,7 +8738,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -8648,7 +8812,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -8722,7 +8886,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -8796,7 +8960,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -8870,7 +9034,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -8944,7 +9108,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -9018,7 +9182,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -9092,7 +9256,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -9166,7 +9330,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -9240,7 +9404,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -9314,7 +9478,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -9388,7 +9552,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -9462,7 +9626,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -9536,7 +9700,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -9610,7 +9774,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -9684,7 +9848,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -9758,7 +9922,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -9832,7 +9996,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -9906,7 +10070,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -9980,7 +10144,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -10054,7 +10218,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -10128,7 +10292,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -10202,7 +10366,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -10276,7 +10440,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -10350,7 +10514,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -10424,7 +10588,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -10498,7 +10662,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -10572,7 +10736,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -10646,7 +10810,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -10720,7 +10884,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -10794,7 +10958,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -10868,7 +11032,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -10942,7 +11106,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11016,7 +11180,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11090,7 +11254,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11164,7 +11328,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -11238,7 +11402,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -11312,7 +11476,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -11386,7 +11550,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -11460,7 +11624,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -11534,7 +11698,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -11608,7 +11772,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -11682,7 +11846,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -11756,7 +11920,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -11830,7 +11994,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -11904,7 +12068,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -11978,7 +12142,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12052,7 +12216,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -12126,7 +12290,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12200,7 +12364,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12274,7 +12438,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -12348,7 +12512,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12422,7 +12586,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -12496,7 +12660,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12570,7 +12734,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12644,7 +12808,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12718,7 +12882,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12792,7 +12956,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12866,7 +13030,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12940,7 +13104,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -13014,7 +13178,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -13088,7 +13252,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -13162,7 +13326,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -13236,7 +13400,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -13310,7 +13474,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -13384,7 +13548,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -13458,7 +13622,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -13532,7 +13696,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -13606,7 +13770,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -13680,7 +13844,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -13754,7 +13918,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -13828,7 +13992,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -13902,7 +14066,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -13976,7 +14140,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -14050,7 +14214,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -14124,7 +14288,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -14198,7 +14362,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -14272,7 +14436,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -14346,7 +14510,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -14420,7 +14584,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -14494,7 +14658,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -14568,7 +14732,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -14642,7 +14806,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -14716,7 +14880,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -14790,7 +14954,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -14864,7 +15028,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -14938,7 +15102,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -15012,7 +15176,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -15086,7 +15250,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -15160,7 +15324,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -15234,7 +15398,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -15308,7 +15472,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -15382,7 +15546,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -15456,7 +15620,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -15530,7 +15694,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -15604,7 +15768,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -15678,7 +15842,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -15752,7 +15916,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -15826,7 +15990,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -15900,7 +16064,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -15974,7 +16138,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -16048,7 +16212,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -16122,7 +16286,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -16196,7 +16360,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -16270,7 +16434,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -16344,7 +16508,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -16418,7 +16582,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -16492,7 +16656,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -16566,7 +16730,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -16640,7 +16804,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -16714,7 +16878,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -16788,7 +16952,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -16862,7 +17026,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -16936,7 +17100,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -17010,7 +17174,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -17084,7 +17248,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -17158,7 +17322,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -17232,7 +17396,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -17306,7 +17470,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -17380,7 +17544,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -17454,7 +17618,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -17528,7 +17692,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -17602,7 +17766,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -17676,7 +17840,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -17750,7 +17914,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -17824,7 +17988,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -17898,7 +18062,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -17972,7 +18136,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -18046,7 +18210,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -18120,7 +18284,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -18194,7 +18358,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -18268,7 +18432,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -18342,7 +18506,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -18416,7 +18580,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -18490,7 +18654,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -18564,7 +18728,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -18638,7 +18802,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -18712,7 +18876,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -18786,7 +18950,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -18860,7 +19024,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -18934,7 +19098,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -19008,7 +19172,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -19082,7 +19246,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -19156,7 +19320,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -19230,7 +19394,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -19304,7 +19468,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -19378,7 +19542,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -19452,7 +19616,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -19526,7 +19690,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -19600,7 +19764,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -19674,7 +19838,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -19748,7 +19912,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -19822,7 +19986,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -19896,7 +20060,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -19970,7 +20134,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -20044,7 +20208,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -20118,7 +20282,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -20192,7 +20356,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -20266,7 +20430,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -20340,7 +20504,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -20414,7 +20578,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -20488,7 +20652,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -20562,7 +20726,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -20636,7 +20800,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -20710,7 +20874,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -20784,7 +20948,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -20858,7 +21022,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -20932,7 +21096,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -21006,7 +21170,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -21080,7 +21244,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -21154,7 +21318,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -21228,7 +21392,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -21302,7 +21466,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -21376,7 +21540,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -21450,7 +21614,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -21524,7 +21688,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -21598,7 +21762,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -21672,7 +21836,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -21746,7 +21910,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -21820,7 +21984,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -21894,7 +22058,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -21968,7 +22132,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -22042,7 +22206,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -22116,7 +22280,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -22190,7 +22354,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -22264,7 +22428,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -22338,7 +22502,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -22412,7 +22576,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -22486,7 +22650,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -22560,7 +22724,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -22634,7 +22798,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -22708,7 +22872,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -22782,7 +22946,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -22856,7 +23020,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -22930,7 +23094,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -23004,7 +23168,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -23078,7 +23242,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -23152,7 +23316,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -23226,7 +23390,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -23300,7 +23464,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -23374,7 +23538,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -23448,7 +23612,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -23522,7 +23686,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -23596,7 +23760,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -23670,7 +23834,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -23744,7 +23908,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -23818,7 +23982,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -23892,7 +24056,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -23966,7 +24130,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -24040,7 +24204,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -24114,7 +24278,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -24188,7 +24352,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -24262,7 +24426,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -24336,7 +24500,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -24410,7 +24574,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -24484,7 +24648,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -24558,7 +24722,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -24632,7 +24796,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -24706,7 +24870,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -24780,7 +24944,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -24854,7 +25018,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -24928,7 +25092,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -25002,7 +25166,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -25076,7 +25240,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -25150,7 +25314,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -25224,7 +25388,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -25298,7 +25462,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -25372,7 +25536,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -25446,7 +25610,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -25520,7 +25684,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -25594,7 +25758,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -25668,7 +25832,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -25742,7 +25906,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -25816,7 +25980,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -25890,7 +26054,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -25964,7 +26128,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -26038,7 +26202,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -26112,7 +26276,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -26186,7 +26350,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -26260,7 +26424,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -26334,7 +26498,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -26408,7 +26572,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -26482,7 +26646,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -26556,7 +26720,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -26630,7 +26794,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -26704,7 +26868,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -26778,7 +26942,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -26852,7 +27016,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -26926,7 +27090,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -27000,7 +27164,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -27074,7 +27238,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -27148,7 +27312,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -27222,7 +27386,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -27296,7 +27460,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -27370,7 +27534,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -27444,7 +27608,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -27518,7 +27682,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -27592,7 +27756,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -27666,7 +27830,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -27740,7 +27904,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -27814,7 +27978,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -27888,7 +28052,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -27962,7 +28126,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -28036,7 +28200,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -28110,7 +28274,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -28184,7 +28348,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -28258,7 +28422,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -28332,7 +28496,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -28406,7 +28570,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -28480,7 +28644,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -28554,7 +28718,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -28628,7 +28792,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="C361">
         <v>0</v>
@@ -28702,7 +28866,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -28776,7 +28940,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -28850,7 +29014,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -28924,7 +29088,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -28998,7 +29162,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -29072,7 +29236,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -29146,7 +29310,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -29220,7 +29384,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -29294,7 +29458,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -29368,7 +29532,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -29442,7 +29606,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -29516,7 +29680,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -29590,7 +29754,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -29664,7 +29828,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -29738,7 +29902,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -29812,7 +29976,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -29886,7 +30050,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -29960,7 +30124,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -30034,7 +30198,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -30108,7 +30272,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -30182,7 +30346,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -30256,7 +30420,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -30330,7 +30494,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -30404,7 +30568,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -30478,7 +30642,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -30552,7 +30716,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -30626,7 +30790,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -30700,7 +30864,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -30774,7 +30938,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -30848,7 +31012,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -30922,7 +31086,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -30996,7 +31160,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -31070,7 +31234,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -31144,7 +31308,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="C395">
         <v>0</v>
@@ -31218,7 +31382,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="C396">
         <v>0</v>
@@ -31292,7 +31456,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -31366,7 +31530,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -31440,7 +31604,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -31514,7 +31678,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C400">
         <v>0</v>
@@ -31588,7 +31752,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -31662,7 +31826,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -31736,7 +31900,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -31810,7 +31974,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -31884,7 +32048,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -31958,7 +32122,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="C406">
         <v>0</v>
@@ -32032,7 +32196,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -32106,7 +32270,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="C408">
         <v>0</v>
@@ -32180,7 +32344,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="C409">
         <v>0</v>
@@ -32254,7 +32418,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="C410">
         <v>0</v>
@@ -32328,7 +32492,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="C411">
         <v>0</v>
@@ -32402,7 +32566,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="C412">
         <v>0</v>
@@ -32476,7 +32640,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="C413">
         <v>0</v>
@@ -32550,7 +32714,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="C414">
         <v>0</v>
@@ -32624,7 +32788,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="C415">
         <v>0</v>
@@ -32698,7 +32862,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C416">
         <v>0</v>
@@ -32772,7 +32936,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C417">
         <v>0</v>
@@ -32846,7 +33010,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -32920,7 +33084,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -32994,7 +33158,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C420">
         <v>0</v>
@@ -33068,7 +33232,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="C421">
         <v>0</v>
@@ -33142,7 +33306,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C422">
         <v>0</v>
@@ -33216,7 +33380,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="C423">
         <v>0</v>
@@ -33290,7 +33454,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="C424">
         <v>0</v>
@@ -33364,7 +33528,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="C425">
         <v>0</v>
@@ -33438,7 +33602,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -33512,7 +33676,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -33586,7 +33750,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="C428">
         <v>0</v>
@@ -33660,7 +33824,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="C429">
         <v>0</v>
@@ -33734,7 +33898,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="C430">
         <v>0</v>
@@ -33808,7 +33972,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="C431">
         <v>0</v>
@@ -33882,7 +34046,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="C432">
         <v>0</v>
@@ -33956,7 +34120,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="C433">
         <v>0</v>
@@ -34030,7 +34194,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -34104,7 +34268,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -34178,7 +34342,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -34252,7 +34416,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="C437">
         <v>0</v>
@@ -34326,7 +34490,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="C438">
         <v>0</v>
@@ -34400,7 +34564,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="C439">
         <v>0</v>
@@ -34474,7 +34638,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="C440">
         <v>0</v>
@@ -34548,7 +34712,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="C441">
         <v>0</v>
@@ -34622,7 +34786,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C442">
         <v>0</v>
@@ -34696,7 +34860,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="C443">
         <v>0</v>
@@ -34770,7 +34934,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C444">
         <v>0</v>
@@ -34844,7 +35008,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="C445">
         <v>0</v>
@@ -34918,7 +35082,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C446">
         <v>0</v>
@@ -34992,7 +35156,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="C447">
         <v>0</v>
@@ -35066,7 +35230,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -35140,7 +35304,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -35214,7 +35378,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="C450">
         <v>0</v>
@@ -35288,7 +35452,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="C451">
         <v>0</v>
@@ -35362,7 +35526,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="C452">
         <v>0</v>
@@ -35436,7 +35600,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="C453">
         <v>0</v>
@@ -35510,7 +35674,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="C454">
         <v>0</v>
@@ -35584,7 +35748,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="C455">
         <v>0</v>
@@ -35658,7 +35822,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="C456">
         <v>0</v>
@@ -35732,7 +35896,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="C457">
         <v>0</v>
@@ -35806,7 +35970,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="C458">
         <v>0</v>
@@ -35880,7 +36044,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="C459">
         <v>0</v>
@@ -35954,7 +36118,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="C460">
         <v>0</v>
@@ -36028,7 +36192,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="C461">
         <v>0</v>
@@ -36102,7 +36266,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="C462">
         <v>0</v>
@@ -36176,7 +36340,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="C463">
         <v>0</v>
@@ -36250,7 +36414,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="C464">
         <v>0</v>
@@ -36324,7 +36488,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="C465">
         <v>0</v>
@@ -36398,7 +36562,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="C466">
         <v>0</v>
@@ -36472,7 +36636,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="C467">
         <v>0</v>
@@ -36546,7 +36710,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="C468">
         <v>0</v>
@@ -36620,7 +36784,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="C469">
         <v>0</v>
@@ -36694,7 +36858,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="C470">
         <v>0</v>
@@ -36768,7 +36932,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="C471">
         <v>0</v>
@@ -36842,7 +37006,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C472">
         <v>0</v>
@@ -36916,7 +37080,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="C473">
         <v>0</v>
@@ -36990,7 +37154,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="C474">
         <v>0</v>
@@ -37064,7 +37228,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="C475">
         <v>0</v>
@@ -37138,7 +37302,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="C476">
         <v>0</v>
@@ -37212,7 +37376,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="C477">
         <v>0</v>
@@ -37286,7 +37450,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="C478">
         <v>0</v>
@@ -37360,7 +37524,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="C479">
         <v>0</v>
@@ -37434,7 +37598,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="C480">
         <v>0</v>
@@ -37508,7 +37672,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="C481">
         <v>0</v>
@@ -37582,7 +37746,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="C482">
         <v>0</v>
@@ -37656,7 +37820,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="C483">
         <v>0</v>
@@ -37730,7 +37894,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="C484">
         <v>0</v>
@@ -37804,7 +37968,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>482</v>
+        <v>505</v>
       </c>
       <c r="C485">
         <v>0</v>
@@ -37878,7 +38042,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="C486">
         <v>0</v>
@@ -37952,7 +38116,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="C487">
         <v>0</v>
@@ -38026,7 +38190,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="C488">
         <v>0</v>
@@ -38100,7 +38264,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="C489">
         <v>0</v>
@@ -38174,7 +38338,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="C490">
         <v>0</v>
@@ -38248,7 +38412,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="C491">
         <v>0</v>
@@ -38322,7 +38486,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="C492">
         <v>0</v>
@@ -38396,7 +38560,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="C493">
         <v>0</v>
@@ -38470,7 +38634,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="C494">
         <v>0</v>
@@ -38544,7 +38708,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="s">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="C495">
         <v>0</v>
@@ -38618,7 +38782,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="C496">
         <v>0</v>
@@ -38692,7 +38856,7 @@
         <v>495</v>
       </c>
       <c r="B497" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="C497">
         <v>0</v>
@@ -38766,7 +38930,7 @@
         <v>496</v>
       </c>
       <c r="B498" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="C498">
         <v>0</v>
@@ -38840,7 +39004,7 @@
         <v>497</v>
       </c>
       <c r="B499" t="s">
-        <v>496</v>
+        <v>519</v>
       </c>
       <c r="C499">
         <v>0</v>
@@ -38914,7 +39078,7 @@
         <v>498</v>
       </c>
       <c r="B500" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="C500">
         <v>0</v>
@@ -38988,7 +39152,7 @@
         <v>499</v>
       </c>
       <c r="B501" t="s">
-        <v>498</v>
+        <v>521</v>
       </c>
       <c r="C501">
         <v>0</v>
@@ -39062,7 +39226,7 @@
         <v>500</v>
       </c>
       <c r="B502" t="s">
-        <v>499</v>
+        <v>522</v>
       </c>
       <c r="C502">
         <v>0</v>
@@ -39136,7 +39300,7 @@
         <v>501</v>
       </c>
       <c r="B503" t="s">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -39210,7 +39374,7 @@
         <v>502</v>
       </c>
       <c r="B504" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -39284,7 +39448,7 @@
         <v>503</v>
       </c>
       <c r="B505" t="s">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="C505">
         <v>0</v>
@@ -39358,7 +39522,7 @@
         <v>504</v>
       </c>
       <c r="B506" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="C506">
         <v>0</v>
@@ -39432,7 +39596,7 @@
         <v>505</v>
       </c>
       <c r="B507" t="s">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="C507">
         <v>0</v>
@@ -39506,7 +39670,7 @@
         <v>506</v>
       </c>
       <c r="B508" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="C508">
         <v>0</v>
@@ -39580,7 +39744,7 @@
         <v>507</v>
       </c>
       <c r="B509" t="s">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="C509">
         <v>0</v>
@@ -39654,7 +39818,7 @@
         <v>508</v>
       </c>
       <c r="B510" t="s">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="C510">
         <v>0</v>
@@ -39728,7 +39892,7 @@
         <v>509</v>
       </c>
       <c r="B511" t="s">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="C511">
         <v>0</v>
@@ -39802,7 +39966,7 @@
         <v>510</v>
       </c>
       <c r="B512" t="s">
-        <v>509</v>
+        <v>532</v>
       </c>
       <c r="C512">
         <v>0</v>
@@ -39876,7 +40040,7 @@
         <v>511</v>
       </c>
       <c r="B513" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="C513">
         <v>0</v>
@@ -39950,7 +40114,7 @@
         <v>512</v>
       </c>
       <c r="B514" t="s">
-        <v>511</v>
+        <v>534</v>
       </c>
       <c r="C514">
         <v>0</v>
@@ -40024,7 +40188,7 @@
         <v>513</v>
       </c>
       <c r="B515" t="s">
-        <v>512</v>
+        <v>535</v>
       </c>
       <c r="C515">
         <v>0</v>
@@ -40098,7 +40262,7 @@
         <v>514</v>
       </c>
       <c r="B516" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -40172,7 +40336,7 @@
         <v>515</v>
       </c>
       <c r="B517" t="s">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="C517">
         <v>0</v>
@@ -40246,7 +40410,7 @@
         <v>516</v>
       </c>
       <c r="B518" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="C518">
         <v>0</v>
@@ -40320,7 +40484,7 @@
         <v>517</v>
       </c>
       <c r="B519" t="s">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="C519">
         <v>0</v>
@@ -40394,7 +40558,7 @@
         <v>518</v>
       </c>
       <c r="B520" t="s">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="C520">
         <v>0</v>
@@ -40468,7 +40632,7 @@
         <v>519</v>
       </c>
       <c r="B521" t="s">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="C521">
         <v>0</v>
@@ -40542,7 +40706,7 @@
         <v>520</v>
       </c>
       <c r="B522" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="C522">
         <v>0</v>
@@ -40616,7 +40780,7 @@
         <v>521</v>
       </c>
       <c r="B523" t="s">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="C523">
         <v>0</v>
@@ -40690,7 +40854,7 @@
         <v>522</v>
       </c>
       <c r="B524" t="s">
-        <v>521</v>
+        <v>544</v>
       </c>
       <c r="C524">
         <v>0</v>
@@ -40764,7 +40928,7 @@
         <v>523</v>
       </c>
       <c r="B525" t="s">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -40838,7 +41002,7 @@
         <v>524</v>
       </c>
       <c r="B526" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="C526">
         <v>0</v>
@@ -40912,7 +41076,7 @@
         <v>525</v>
       </c>
       <c r="B527" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="C527">
         <v>0</v>
@@ -40986,7 +41150,7 @@
         <v>526</v>
       </c>
       <c r="B528" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
       <c r="C528">
         <v>0</v>
@@ -41060,7 +41224,7 @@
         <v>527</v>
       </c>
       <c r="B529" t="s">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -41134,7 +41298,7 @@
         <v>528</v>
       </c>
       <c r="B530" t="s">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="C530">
         <v>0</v>
@@ -41208,7 +41372,7 @@
         <v>529</v>
       </c>
       <c r="B531" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
       <c r="C531">
         <v>0</v>
@@ -41282,7 +41446,7 @@
         <v>530</v>
       </c>
       <c r="B532" t="s">
-        <v>529</v>
+        <v>552</v>
       </c>
       <c r="C532">
         <v>0</v>
@@ -41356,7 +41520,7 @@
         <v>531</v>
       </c>
       <c r="B533" t="s">
-        <v>530</v>
+        <v>553</v>
       </c>
       <c r="C533">
         <v>0</v>
@@ -41430,7 +41594,7 @@
         <v>532</v>
       </c>
       <c r="B534" t="s">
-        <v>531</v>
+        <v>554</v>
       </c>
       <c r="C534">
         <v>0</v>
@@ -41504,7 +41668,7 @@
         <v>533</v>
       </c>
       <c r="B535" t="s">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="C535">
         <v>0</v>
@@ -41578,7 +41742,7 @@
         <v>534</v>
       </c>
       <c r="B536" t="s">
-        <v>533</v>
+        <v>556</v>
       </c>
       <c r="C536">
         <v>0</v>
@@ -41652,7 +41816,7 @@
         <v>535</v>
       </c>
       <c r="B537" t="s">
-        <v>534</v>
+        <v>557</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -41726,7 +41890,7 @@
         <v>536</v>
       </c>
       <c r="B538" t="s">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -41800,7 +41964,7 @@
         <v>537</v>
       </c>
       <c r="B539" t="s">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="C539">
         <v>0</v>
@@ -41874,7 +42038,7 @@
         <v>538</v>
       </c>
       <c r="B540" t="s">
-        <v>537</v>
+        <v>560</v>
       </c>
       <c r="C540">
         <v>0</v>
@@ -41948,7 +42112,7 @@
         <v>539</v>
       </c>
       <c r="B541" t="s">
-        <v>538</v>
+        <v>561</v>
       </c>
       <c r="C541">
         <v>0</v>
@@ -42022,7 +42186,7 @@
         <v>540</v>
       </c>
       <c r="B542" t="s">
-        <v>539</v>
+        <v>562</v>
       </c>
       <c r="C542">
         <v>0</v>
@@ -42096,7 +42260,7 @@
         <v>541</v>
       </c>
       <c r="B543" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="C543">
         <v>0</v>
@@ -42170,7 +42334,7 @@
         <v>542</v>
       </c>
       <c r="B544" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="C544">
         <v>0</v>
@@ -42244,7 +42408,7 @@
         <v>543</v>
       </c>
       <c r="B545" t="s">
-        <v>542</v>
+        <v>565</v>
       </c>
       <c r="C545">
         <v>0</v>
@@ -42318,7 +42482,7 @@
         <v>544</v>
       </c>
       <c r="B546" t="s">
-        <v>543</v>
+        <v>566</v>
       </c>
       <c r="C546">
         <v>0</v>
@@ -42392,7 +42556,7 @@
         <v>545</v>
       </c>
       <c r="B547" t="s">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="C547">
         <v>0</v>
@@ -42466,7 +42630,7 @@
         <v>546</v>
       </c>
       <c r="B548" t="s">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="C548">
         <v>0</v>
@@ -42540,7 +42704,7 @@
         <v>547</v>
       </c>
       <c r="B549" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="C549">
         <v>0</v>
